--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484276_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484276_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7256</v>
+        <v>2.9944</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0517</v>
+        <v>2.3749</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.6194</v>
       </c>
       <c r="G2" t="n">
         <v>2.8884</v>
@@ -610,13 +610,13 @@
         <v>2.3441</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4078</v>
+        <v>-0.139</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2529</v>
+        <v>0.0703</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1549</v>
+        <v>-0.2093</v>
       </c>
       <c r="V2" t="n">
         <v>-0.7318</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6748</v>
+        <v>2.3018</v>
       </c>
       <c r="E3" t="n">
-        <v>3.29</v>
+        <v>3.1077</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6153</v>
+        <v>-0.8058999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>3.8545</v>
@@ -688,13 +688,13 @@
         <v>1.7581</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0036</v>
+        <v>0.6307</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9053</v>
+        <v>0.723</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0983</v>
+        <v>-0.0924</v>
       </c>
       <c r="V3" t="n">
         <v>-2.7693</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7986</v>
+        <v>1.4312</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9273</v>
+        <v>-0.9679</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7259</v>
+        <v>2.3991</v>
       </c>
       <c r="G4" t="n">
         <v>-1.4401</v>
@@ -766,13 +766,13 @@
         <v>1.9534</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4341</v>
+        <v>0.0667</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0221</v>
+        <v>-0.0185</v>
       </c>
       <c r="U4" t="n">
-        <v>0.412</v>
+        <v>0.0851</v>
       </c>
       <c r="V4" t="n">
         <v>1.8279</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7133</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7011</v>
+        <v>2.3572</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9878</v>
+        <v>-1.7972</v>
       </c>
       <c r="G5" t="n">
         <v>3.0061</v>
@@ -844,13 +844,13 @@
         <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4848</v>
+        <v>0.3315</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9053</v>
+        <v>0.5614</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4205</v>
+        <v>-0.2299</v>
       </c>
       <c r="V5" t="n">
         <v>-1.6056</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2017</v>
+        <v>0.4584</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1768</v>
+        <v>0.379</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0249</v>
+        <v>0.0794</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3815</v>
@@ -922,13 +922,13 @@
         <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5497</v>
+        <v>-0.293</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2229</v>
+        <v>0.4251</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7726</v>
+        <v>-0.7181</v>
       </c>
       <c r="V6" t="n">
         <v>1.3283</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.17</v>
+        <v>0.3256</v>
       </c>
       <c r="E7" t="n">
-        <v>0.548</v>
+        <v>0.6492</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3781</v>
+        <v>-0.3236</v>
       </c>
       <c r="G7" t="n">
         <v>0.3715</v>
@@ -1000,13 +1000,13 @@
         <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6102</v>
+        <v>-0.4547</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1678</v>
+        <v>-0.0667</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4424</v>
+        <v>-0.388</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1773</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.866</v>
+        <v>-0.6015</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7235</v>
+        <v>-1.6224</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8575</v>
+        <v>1.0209</v>
       </c>
       <c r="G8" t="n">
         <v>-0.477</v>
@@ -1078,13 +1078,13 @@
         <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.389</v>
+        <v>-0.1245</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2145</v>
+        <v>-0.1134</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1745</v>
+        <v>-0.0111</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3207</v>
+        <v>-2.6258</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6015</v>
+        <v>-1.7432</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7191</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>-2.3824</v>
@@ -1156,13 +1156,13 @@
         <v>2.1488</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1832</v>
+        <v>-0.4884</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0246</v>
+        <v>-0.1663</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1586</v>
+        <v>-0.322</v>
       </c>
       <c r="V9" t="n">
         <v>-0.7318</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3161</v>
+        <v>-3.7654</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6974</v>
+        <v>-1.6369</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6187</v>
+        <v>-2.1285</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3235</v>
@@ -1234,13 +1234,13 @@
         <v>2.1488</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.632</v>
+        <v>-1.0813</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3878</v>
+        <v>-0.3272</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2443</v>
+        <v>-0.754</v>
       </c>
       <c r="V10" t="n">
         <v>-2.3373</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.046</v>
+        <v>-9.7384</v>
       </c>
       <c r="E11" t="n">
-        <v>-9.2867</v>
+        <v>-8.761200000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7593</v>
+        <v>-0.9772</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4874</v>
@@ -1312,13 +1312,13 @@
         <v>2.5395</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5443</v>
+        <v>-0.2367</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0438</v>
+        <v>0.4817</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5004999999999999</v>
+        <v>-0.7183</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3959</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.264800000000001</v>
+        <v>-8.659699999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.468800000000001</v>
+        <v>-5.863600000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7961</v>
+        <v>-2.7962</v>
       </c>
       <c r="G12" t="n">
         <v>3.6286</v>
@@ -1390,10 +1390,10 @@
         <v>16.6042</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.3937</v>
+        <v>-1.7887</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9642000000000003</v>
+        <v>1.5694</v>
       </c>
       <c r="U12" t="n">
         <v>-3.358</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.5582</v>
+        <v>6.187</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1769</v>
+        <v>2.0758</v>
       </c>
       <c r="F13" t="n">
-        <v>3.3813</v>
+        <v>4.1112</v>
       </c>
       <c r="G13" t="n">
         <v>2.689</v>
@@ -1468,13 +1468,13 @@
         <v>3.1255</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0407</v>
+        <v>0.5881</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3469</v>
+        <v>0.2457</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3876</v>
+        <v>0.3424</v>
       </c>
       <c r="V13" t="n">
         <v>2.7145</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5171</v>
+        <v>4.0572</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7289</v>
+        <v>2.5155</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7882</v>
+        <v>1.5417</v>
       </c>
       <c r="G14" t="n">
         <v>5.2459</v>
@@ -1546,13 +1546,13 @@
         <v>2.9301</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2757</v>
+        <v>1.8159</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2343</v>
+        <v>1.021</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0414</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-1.0511</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>A. PEIRO COSMO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0133</v>
+        <v>2.6626</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0399</v>
+        <v>2.792</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9734</v>
+        <v>-0.1294</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8624000000000001</v>
+        <v>-0.768</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9041</v>
+        <v>0.2709</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.7665</v>
+        <v>-1.0389</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5821</v>
+        <v>0.9448</v>
       </c>
       <c r="K15" t="n">
-        <v>0.779</v>
+        <v>1.5784</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.361</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2803</v>
+        <v>-1.7127</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1251</v>
+        <v>-1.3075</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4054</v>
+        <v>-0.4052</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9534</v>
+        <v>0.586</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9222</v>
+        <v>0.13</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6219</v>
+        <v>0.1095</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3003</v>
+        <v>0.0206</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2.7145</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.7145</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. PEIRO COSMO</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6449</v>
+        <v>2.0079</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2864</v>
+        <v>0.6828</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6415</v>
+        <v>1.325</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.768</v>
+        <v>-3.145</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2709</v>
+        <v>-1.2026</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0389</v>
+        <v>-1.9424</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9448</v>
+        <v>-1.4272</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5784</v>
+        <v>0.5142</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-1.9414</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7127</v>
+        <v>-1.7178</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3075</v>
+        <v>-1.7168</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4052</v>
+        <v>-0.001</v>
       </c>
       <c r="P16" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5627</v>
+        <v>2.7348</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8875999999999999</v>
+        <v>0.9575</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3961</v>
+        <v>0.6495</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4915</v>
+        <v>0.308</v>
       </c>
       <c r="V16" t="n">
-        <v>2.7145</v>
+        <v>2.4373</v>
       </c>
       <c r="W16" t="n">
-        <v>2.7145</v>
+        <v>2.4373</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4945</v>
+        <v>1.8642</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6828</v>
+        <v>-0.1624</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8116</v>
+        <v>2.0265</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.145</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2026</v>
+        <v>0.9041</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.9424</v>
+        <v>-1.7665</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.4272</v>
+        <v>-0.5821</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5142</v>
+        <v>0.779</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.9414</v>
+        <v>-1.361</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7178</v>
+        <v>-0.2803</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7168</v>
+        <v>0.1251</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.001</v>
+        <v>-0.4054</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7581</v>
+        <v>1.9534</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7348</v>
+        <v>1.9534</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4441</v>
+        <v>0.7731</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6495</v>
+        <v>0.4197</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2054</v>
+        <v>0.3534</v>
       </c>
       <c r="V17" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6945</v>
+        <v>0.9254</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9944</v>
+        <v>0.7922</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2999</v>
+        <v>0.1332</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0342</v>
@@ -1858,13 +1858,13 @@
         <v>0.9767</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0292</v>
+        <v>0.26</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5944</v>
+        <v>0.3921</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5652</v>
+        <v>-0.1321</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2772</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.066</v>
+        <v>0.3432</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2978</v>
+        <v>-1.59</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2318</v>
+        <v>1.9332</v>
       </c>
       <c r="G19" t="n">
         <v>0.4181</v>
@@ -1936,13 +1936,13 @@
         <v>3.3208</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.898</v>
+        <v>0.5111</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1924</v>
+        <v>0.5154</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7056</v>
+        <v>-0.0043</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1651</v>
+        <v>-0.8812</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8753</v>
+        <v>-0.673</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2899</v>
+        <v>-0.2082</v>
       </c>
       <c r="G20" t="n">
         <v>-1.038</v>
@@ -2014,13 +2014,13 @@
         <v>0.1953</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3224</v>
+        <v>-0.0385</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2421</v>
+        <v>-0.0399</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0803</v>
+        <v>0.0014</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2748</v>
+        <v>-1.175</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8074</v>
+        <v>-0.7063</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4674</v>
+        <v>-0.4687</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6354</v>
@@ -2092,13 +2092,13 @@
         <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4072</v>
+        <v>0.5069</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0083</v>
+        <v>0.1095</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3988</v>
+        <v>0.3975</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2186</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4013</v>
+        <v>-1.3002</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7501</v>
+        <v>-1.649</v>
       </c>
       <c r="F22" t="n">
         <v>0.3488</v>
@@ -2170,10 +2170,10 @@
         <v>0.586</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0605</v>
+        <v>0.1616</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2421</v>
+        <v>-0.141</v>
       </c>
       <c r="U22" t="n">
         <v>0.3026</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7504</v>
+        <v>-2.0556</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3827</v>
+        <v>-1.2816</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3677</v>
+        <v>-0.774</v>
       </c>
       <c r="G23" t="n">
         <v>-3.4274</v>
@@ -2248,13 +2248,13 @@
         <v>1.9534</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5965</v>
+        <v>0.0984</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0246</v>
+        <v>0.0765</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5718</v>
+        <v>0.0219</v>
       </c>
       <c r="V23" t="n">
         <v>1.2735</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>9.264900000000001</v>
+        <v>12.6355</v>
       </c>
       <c r="E24" t="n">
-        <v>2.795999999999999</v>
+        <v>2.796</v>
       </c>
       <c r="F24" t="n">
-        <v>6.4687</v>
+        <v>9.839300000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-3.6286</v>
@@ -2296,7 +2296,7 @@
         <v>5.1408</v>
       </c>
       <c r="I24" t="n">
-        <v>-8.769299999999998</v>
+        <v>-8.769299999999999</v>
       </c>
       <c r="J24" t="n">
         <v>6.012800000000002</v>
@@ -2311,7 +2311,7 @@
         <v>-9.641500000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>-5.587</v>
+        <v>-5.586999999999999</v>
       </c>
       <c r="O24" t="n">
         <v>-4.0544</v>
@@ -2326,13 +2326,13 @@
         <v>20.5108</v>
       </c>
       <c r="S24" t="n">
-        <v>2.3937</v>
+        <v>5.764099999999999</v>
       </c>
       <c r="T24" t="n">
         <v>3.358</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9643</v>
+        <v>2.4063</v>
       </c>
       <c r="V24" t="n">
         <v>6.5929</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484276_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484276_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.7318</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484276_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-2.4373</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484276_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484276_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.7145</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484276_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.1097</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484276_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,11 +1047,16 @@
       <c r="X7" t="n">
         <v>-0.1773</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484276_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. JOVER SANS</t>
+          <t>A. BENNASSAR ROSSELLÓ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1068,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6015</v>
+        <v>0.307</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6224</v>
+        <v>0.307</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0209</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.477</v>
+        <v>0.307</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4635</v>
+        <v>0.307</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0134</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5322</v>
+        <v>0.307</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0205</v>
+        <v>0.307</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5527</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0553</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.484</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5393</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1245</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1134</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0111</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1094,12 +1129,17 @@
       </c>
       <c r="X8" t="n">
         <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484276_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. BENNASSAR ROSSELLÓ</t>
+          <t>P. JOVER SANS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6258</v>
+        <v>-0.6015</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7432</v>
+        <v>-1.6224</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8826000000000001</v>
+        <v>1.0209</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3824</v>
+        <v>-0.477</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.3016</v>
+        <v>-0.4635</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.0134</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4049</v>
+        <v>-0.5322</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.999</v>
+        <v>0.0205</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5942</v>
+        <v>-0.5527</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9775</v>
+        <v>0.0553</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3026</v>
+        <v>-0.484</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0.5393</v>
       </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R9" t="n">
         <v>0.9767</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-1.1721</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.1488</v>
-      </c>
       <c r="S9" t="n">
-        <v>-0.4884</v>
+        <v>-0.1245</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1663</v>
+        <v>-0.1134</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.322</v>
+        <v>-0.0111</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7318</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.7318</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484276_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. DIALLO BADJI</t>
+          <t>A. BENNASSAR ROSSELLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,40 +1234,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7654</v>
+        <v>-2.9328</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6369</v>
+        <v>-2.0502</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1285</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3235</v>
+        <v>-2.6894</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7838000000000001</v>
+        <v>-2.6086</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5397</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4148</v>
+        <v>-0.7118</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1241</v>
+        <v>-1.306</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5389</v>
+        <v>0.5942</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9087</v>
+        <v>-1.9775</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9079</v>
+        <v>-1.3026</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0008</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P10" t="n">
         <v>0.9767</v>
@@ -1234,28 +1279,33 @@
         <v>2.1488</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0813</v>
+        <v>-0.4884</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3272</v>
+        <v>-0.1663</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.754</v>
+        <v>-0.322</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.3373</v>
+        <v>-0.7318</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.6146</v>
+        <v>-0.7318</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484276_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. ZUSTOVICH</t>
+          <t>M. DIALLO BADJI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.7384</v>
+        <v>-3.7654</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.761200000000001</v>
+        <v>-1.6369</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9772</v>
+        <v>-2.1285</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4874</v>
+        <v>-1.3235</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.6439</v>
+        <v>-0.7838000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1565</v>
+        <v>-0.5397</v>
       </c>
       <c r="J11" t="n">
-        <v>0.915</v>
+        <v>-0.4148</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.5682</v>
+        <v>0.1241</v>
       </c>
       <c r="L11" t="n">
-        <v>2.4832</v>
+        <v>-0.5389</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4024</v>
+        <v>-0.9087</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.0757</v>
+        <v>-0.9079</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6733</v>
+        <v>-0.0008</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.6184</v>
+        <v>0.9767</v>
       </c>
       <c r="Q11" t="n">
-        <v>-10.1578</v>
+        <v>-1.1721</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5395</v>
+        <v>2.1488</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2367</v>
+        <v>-1.0813</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4817</v>
+        <v>-0.3272</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7183</v>
+        <v>-0.754</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.3959</v>
+        <v>-2.3373</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.3959</v>
+        <v>-2.6146</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484276_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>E. ZUSTOVICH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,151 +1400,157 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.659699999999999</v>
+        <v>-9.7384</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.863600000000001</v>
+        <v>-8.761200000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7962</v>
+        <v>-0.9772</v>
       </c>
       <c r="G12" t="n">
-        <v>3.6286</v>
+        <v>-0.4874</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.1405</v>
+        <v>-3.6439</v>
       </c>
       <c r="I12" t="n">
-        <v>8.769299999999999</v>
+        <v>3.1565</v>
       </c>
       <c r="J12" t="n">
-        <v>9.641500000000001</v>
+        <v>0.915</v>
       </c>
       <c r="K12" t="n">
-        <v>5.5871</v>
+        <v>-1.5682</v>
       </c>
       <c r="L12" t="n">
-        <v>4.054500000000001</v>
+        <v>2.4832</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.0129</v>
+        <v>-1.4024</v>
       </c>
       <c r="N12" t="n">
-        <v>-10.7276</v>
+        <v>-2.0757</v>
       </c>
       <c r="O12" t="n">
-        <v>4.714700000000001</v>
+        <v>0.6733</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.907</v>
+        <v>-7.6184</v>
       </c>
       <c r="Q12" t="n">
-        <v>-20.5111</v>
+        <v>-10.1578</v>
       </c>
       <c r="R12" t="n">
-        <v>16.6042</v>
+        <v>2.5395</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7887</v>
+        <v>-0.2367</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5694</v>
+        <v>0.4817</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.358</v>
+        <v>-0.7183</v>
       </c>
       <c r="V12" t="n">
-        <v>-6.5928</v>
+        <v>-1.3959</v>
       </c>
       <c r="W12" t="n">
-        <v>3.4364</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-10.0293</v>
+        <v>-1.3959</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484276_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C.B. GRANOLLERS</t>
+          <t>CB ANDRATX</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.187</v>
+        <v>-8.659699999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0758</v>
+        <v>-5.863600000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>4.1112</v>
+        <v>-2.7962</v>
       </c>
       <c r="G13" t="n">
-        <v>2.689</v>
+        <v>3.6286</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8639</v>
+        <v>-5.140499999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1749</v>
+        <v>8.769299999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>2.1005</v>
+        <v>9.6416</v>
       </c>
       <c r="K13" t="n">
-        <v>2.2742</v>
+        <v>5.5871</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1737</v>
+        <v>4.054500000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5885</v>
+        <v>-6.0129</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5897</v>
+        <v>-10.7276</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0012</v>
+        <v>4.714700000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1953</v>
+        <v>-3.907</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.9301</v>
+        <v>-20.5111</v>
       </c>
       <c r="R13" t="n">
-        <v>3.1255</v>
+        <v>16.6042</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5881</v>
+        <v>-1.7887</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2457</v>
+        <v>1.5694</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3424</v>
+        <v>-3.358000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>2.7145</v>
+        <v>-6.5928</v>
       </c>
       <c r="W13" t="n">
-        <v>2.6596</v>
+        <v>3.4364</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0549</v>
-      </c>
+        <v>-10.0293</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>J. JUAREZ GIMENEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0572</v>
+        <v>6.187</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5155</v>
+        <v>2.0758</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5417</v>
+        <v>4.1112</v>
       </c>
       <c r="G14" t="n">
-        <v>5.2459</v>
+        <v>2.689</v>
       </c>
       <c r="H14" t="n">
-        <v>4.7481</v>
+        <v>2.8639</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4978</v>
+        <v>-0.1749</v>
       </c>
       <c r="J14" t="n">
-        <v>5.6013</v>
+        <v>2.1005</v>
       </c>
       <c r="K14" t="n">
-        <v>4.8325</v>
+        <v>2.2742</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7688</v>
+        <v>-0.1737</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.3554</v>
+        <v>0.5885</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0844</v>
+        <v>0.5897</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.271</v>
+        <v>-0.0012</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.9534</v>
+        <v>0.1953</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.8836</v>
+        <v>-2.9301</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9301</v>
+        <v>3.1255</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8159</v>
+        <v>0.5881</v>
       </c>
       <c r="T14" t="n">
-        <v>1.021</v>
+        <v>0.2457</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.3424</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.0511</v>
+        <v>2.7145</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7768</v>
+        <v>2.6596</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.8279</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484276_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. PEIRO COSMO</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6626</v>
+        <v>4.0572</v>
       </c>
       <c r="E15" t="n">
-        <v>2.792</v>
+        <v>2.5155</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1294</v>
+        <v>1.5417</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.768</v>
+        <v>5.2459</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2709</v>
+        <v>4.7481</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.0389</v>
+        <v>0.4978</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9448</v>
+        <v>5.6013</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5784</v>
+        <v>4.8325</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.7688</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7127</v>
+        <v>-0.3554</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3075</v>
+        <v>-0.0844</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4052</v>
+        <v>-0.271</v>
       </c>
       <c r="P15" t="n">
-        <v>0.586</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>-4.8836</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5627</v>
+        <v>2.9301</v>
       </c>
       <c r="S15" t="n">
-        <v>0.13</v>
+        <v>1.8159</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1095</v>
+        <v>1.021</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0206</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>2.7145</v>
+        <v>-1.0511</v>
       </c>
       <c r="W15" t="n">
-        <v>2.7145</v>
+        <v>0.7768</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484276_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>A. PEIRO COSMO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1728,72 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0079</v>
+        <v>2.6626</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6828</v>
+        <v>2.792</v>
       </c>
       <c r="F16" t="n">
-        <v>1.325</v>
+        <v>-0.1294</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.145</v>
+        <v>-0.768</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.2026</v>
+        <v>0.2709</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.9424</v>
+        <v>-1.0389</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.4272</v>
+        <v>0.9448</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5142</v>
+        <v>1.5784</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.9414</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7178</v>
+        <v>-1.7127</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.7168</v>
+        <v>-1.3075</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.001</v>
+        <v>-0.4052</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7348</v>
+        <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9575</v>
+        <v>0.13</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6495</v>
+        <v>0.1095</v>
       </c>
       <c r="U16" t="n">
-        <v>0.308</v>
+        <v>0.0206</v>
       </c>
       <c r="V16" t="n">
-        <v>2.4373</v>
+        <v>2.7145</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4373</v>
+        <v>2.7145</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484276_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1797,11 +1873,16 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484276_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>A. VINALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9254</v>
+        <v>1.3939</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7922</v>
+        <v>0.0689</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1332</v>
+        <v>1.325</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0342</v>
+        <v>-3.759</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1011</v>
+        <v>-1.8166</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1352</v>
+        <v>-1.9424</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0642</v>
+        <v>-2.0412</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0642</v>
+        <v>-0.0998</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-1.9414</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0984</v>
+        <v>-1.7178</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-1.7168</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1352</v>
+        <v>-0.001</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9767</v>
+        <v>2.7348</v>
       </c>
       <c r="S18" t="n">
-        <v>0.26</v>
+        <v>0.9575</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3921</v>
+        <v>0.6495</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1321</v>
+        <v>0.308</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2772</v>
+        <v>2.4373</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6642</v>
+        <v>2.4373</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484276_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>M. TORNE DELAURENS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3432</v>
+        <v>0.9254</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.59</v>
+        <v>0.7922</v>
       </c>
       <c r="F19" t="n">
-        <v>1.9332</v>
+        <v>0.1332</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4181</v>
+        <v>-0.0342</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8764</v>
+        <v>0.1011</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4583</v>
+        <v>-0.1352</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8015</v>
+        <v>1.0642</v>
       </c>
       <c r="K19" t="n">
-        <v>1.989</v>
+        <v>1.0642</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1875</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3834</v>
+        <v>-1.0984</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1125</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2708</v>
+        <v>-0.1352</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.3208</v>
+        <v>0.9767</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5111</v>
+        <v>0.26</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5154</v>
+        <v>0.3921</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0043</v>
+        <v>-0.1321</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484276_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MARTÍN ADELANTADO</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +2060,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8812</v>
+        <v>0.614</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.673</v>
+        <v>0.614</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2082</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.038</v>
+        <v>0.614</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1758</v>
+        <v>0.614</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2138</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6332</v>
+        <v>0.614</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0409</v>
+        <v>0.614</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6741</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4049</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1348</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5397</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0385</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0399</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0014</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2030,12 +2121,17 @@
       </c>
       <c r="X20" t="n">
         <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484276_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.175</v>
+        <v>0.3432</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7063</v>
+        <v>-1.59</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4687</v>
+        <v>1.9332</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6354</v>
+        <v>0.4181</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0412</v>
+        <v>0.8764</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5942</v>
+        <v>-0.4583</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8158</v>
+        <v>1.8015</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8967000000000001</v>
+        <v>1.989</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0809</v>
+        <v>-0.1875</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8196</v>
+        <v>-1.3834</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1445</v>
+        <v>-1.1125</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6751</v>
+        <v>-0.2708</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1721</v>
+        <v>-0.586</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1721</v>
+        <v>3.3208</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5069</v>
+        <v>0.5111</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1095</v>
+        <v>0.5154</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3975</v>
+        <v>-0.0043</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484276_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. MASPONS MOLINS</t>
+          <t>A. MARTIN ADELANTADO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2226,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3002</v>
+        <v>-0.8812</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.649</v>
+        <v>-0.673</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3488</v>
+        <v>-0.2082</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0712</v>
+        <v>-1.038</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.437</v>
+        <v>0.1758</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6342</v>
+        <v>-1.2138</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5313</v>
+        <v>-0.6332</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5718</v>
+        <v>0.0409</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0405</v>
+        <v>-0.6741</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5399</v>
+        <v>-0.4049</v>
       </c>
       <c r="N22" t="n">
         <v>0.1348</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6747</v>
+        <v>-0.5397</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1616</v>
+        <v>-0.0385</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.141</v>
+        <v>-0.0399</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3026</v>
+        <v>0.0014</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2186,12 +2287,17 @@
       </c>
       <c r="X22" t="n">
         <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484276_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>M. SALMERON SEGU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0556</v>
+        <v>-1.175</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2816</v>
+        <v>-0.7063</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.774</v>
+        <v>-0.4687</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.4274</v>
+        <v>-1.6354</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.1187</v>
+        <v>-1.0412</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.3087</v>
+        <v>-0.5942</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5099</v>
+        <v>-0.8158</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.8762</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.0809</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.9176</v>
+        <v>-0.8196</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2425</v>
+        <v>-0.1445</v>
       </c>
       <c r="O23" t="n">
         <v>-0.6751</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0984</v>
+        <v>0.5069</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0765</v>
+        <v>0.1095</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0219</v>
+        <v>0.3975</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2735</v>
+        <v>-1.2186</v>
       </c>
       <c r="W23" t="n">
-        <v>2.1052</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.8317</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484276_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>I. MASPONS MOLINS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,235 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-1.3002</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.649</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.0712</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.437</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.6342</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.5313</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.5718</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.5399</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.1348</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.6747</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.1616</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.141</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484276_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>C. HOMS LORENZO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-2.0556</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-1.2816</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.774</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-3.4274</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-2.1187</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-1.3087</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-1.5099</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.8762</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.6336000000000001</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.9176</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.2425</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.6751</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.0984</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.0765</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.2735</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.1052</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.8317</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484276_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>12.6355</v>
       </c>
-      <c r="E24" t="n">
-        <v>2.796</v>
-      </c>
-      <c r="F24" t="n">
+      <c r="E26" t="n">
+        <v>2.7961</v>
+      </c>
+      <c r="F26" t="n">
         <v>9.839300000000001</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G26" t="n">
         <v>-3.6286</v>
       </c>
-      <c r="H24" t="n">
-        <v>5.1408</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="H26" t="n">
+        <v>5.140800000000002</v>
+      </c>
+      <c r="I26" t="n">
         <v>-8.769299999999999</v>
       </c>
-      <c r="J24" t="n">
-        <v>6.012800000000002</v>
-      </c>
-      <c r="K24" t="n">
+      <c r="J26" t="n">
+        <v>6.0128</v>
+      </c>
+      <c r="K26" t="n">
         <v>10.7277</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L26" t="n">
         <v>-4.714700000000001</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M26" t="n">
         <v>-9.641500000000001</v>
       </c>
-      <c r="N24" t="n">
-        <v>-5.586999999999999</v>
-      </c>
-      <c r="O24" t="n">
+      <c r="N26" t="n">
+        <v>-5.587</v>
+      </c>
+      <c r="O26" t="n">
         <v>-4.0544</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P26" t="n">
         <v>3.9068</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q26" t="n">
         <v>-16.6041</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R26" t="n">
         <v>20.5108</v>
       </c>
-      <c r="S24" t="n">
-        <v>5.764099999999999</v>
-      </c>
-      <c r="T24" t="n">
+      <c r="S26" t="n">
+        <v>5.7641</v>
+      </c>
+      <c r="T26" t="n">
         <v>3.358</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U26" t="n">
         <v>2.4063</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V26" t="n">
         <v>6.5929</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W26" t="n">
         <v>10.0292</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X26" t="n">
         <v>-3.4364</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
